--- a/rules/CORE-002064/positive/01/data/CORE-002064-positive-01.xlsx
+++ b/rules/CORE-002064/positive/01/data/CORE-002064-positive-01.xlsx
@@ -1,90 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ts.xpt" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
@@ -104,23 +77,90 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -445,235 +485,366 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-4</v>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>sdtmig</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Filename</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameters</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>TSSEQ</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TSGRPID</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>TSPARM</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>TSVAL</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>TSVALNF</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TSVALCD</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>TSVCDREF</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>TSVCDVER</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="6" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="6" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="6" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="6" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="6" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="6" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="6" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <v>Version of the Reference Terminology</v>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Group ID</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Short Name</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Parameter Value</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Parameter Null Flavor</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Parameter Value Code</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Name of the Reference Terminology</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Version of the Reference Terminology</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <v>Char</v>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="4" t="str">
-        <v>TRT</v>
-      </c>
-      <c r="F5" s="4" t="str">
-        <v>Extension Trial Indicator</v>
-      </c>
-      <c r="G5" s="4" t="str">
-        <v>DI(DEHYDROABIETYL)AMINE ACETATE</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <v>00000UNII1</v>
-      </c>
+      <c r="D5" s="4" t="str"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Extension Trial Indicator</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DI(DEHYDROABIETYL)AMINE ACETATE</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>00000UNII1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Investigational Therapy or Treatment</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>